--- a/table_from_link/30448613_table3.xlsx
+++ b/table_from_link/30448613_table3.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Closest  gene</t>
+          <t>Closest gene</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,17 +434,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Gene  expression</t>
+          <t>Gene expression</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Brain  region</t>
+          <t>Brain region</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>β^</t>
+          <t>β ^</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.36×10−8</t>
+          <t>1.36×10 −8</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.11×10−5</t>
+          <t>1.11×10 −5</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.94×10−6</t>
+          <t>3.94×10 −6</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.64×10−5</t>
+          <t>1.64×10 −5</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.96×10−5</t>
+          <t>1.96×10 −5</t>
         </is>
       </c>
     </row>

--- a/table_from_link/30448613_table3.xlsx
+++ b/table_from_link/30448613_table3.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>IGAP SNP</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Closest gene</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Closest  gene</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Probe set ID a</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Gene expression</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Brain region</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>β ^</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gene  expression</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Brain  region</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>β^</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P-value b</t>
         </is>
@@ -523,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.36×10 −8</t>
+          <t>1.36×10−8</t>
         </is>
       </c>
     </row>
@@ -552,7 +564,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.11×10 −5</t>
+          <t>1.11×10−5</t>
         </is>
       </c>
     </row>
@@ -626,7 +638,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.94×10 −6</t>
+          <t>3.94×10−6</t>
         </is>
       </c>
     </row>
@@ -663,7 +675,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.64×10 −5</t>
+          <t>1.64×10−5</t>
         </is>
       </c>
     </row>
@@ -700,7 +712,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.96×10 −5</t>
+          <t>1.96×10−5</t>
         </is>
       </c>
     </row>

--- a/table_from_link/30448613_table3.xlsx
+++ b/table_from_link/30448613_table3.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Closest  gene</t>
+          <t>Closest gene</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,17 +434,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Gene  expression</t>
+          <t>Gene expression</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Brain  region</t>
+          <t>Brain region</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>β^</t>
+          <t>β ^</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.36×10−8</t>
+          <t>1.36×10 −8</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.11×10−5</t>
+          <t>1.11×10 −5</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.94×10−6</t>
+          <t>3.94×10 −6</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.64×10−5</t>
+          <t>1.64×10 −5</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.96×10−5</t>
+          <t>1.96×10 −5</t>
         </is>
       </c>
     </row>

--- a/table_from_link/30448613_table3.xlsx
+++ b/table_from_link/30448613_table3.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>IGAP SNP</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Closest  gene</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Closest gene</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Probe set ID a</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Gene  expression</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Brain  region</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>β^</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Gene expression</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Brain region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>β ^</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>P-value b</t>
         </is>
@@ -535,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.36×10−8</t>
+          <t>1.36×10 −8</t>
         </is>
       </c>
     </row>
@@ -564,7 +552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.11×10−5</t>
+          <t>1.11×10 −5</t>
         </is>
       </c>
     </row>
@@ -638,7 +626,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.94×10−6</t>
+          <t>3.94×10 −6</t>
         </is>
       </c>
     </row>
@@ -675,7 +663,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.64×10−5</t>
+          <t>1.64×10 −5</t>
         </is>
       </c>
     </row>
@@ -712,7 +700,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.96×10−5</t>
+          <t>1.96×10 −5</t>
         </is>
       </c>
     </row>
